--- a/public/sample/경인쇄 16절.xlsx
+++ b/public/sample/경인쇄 16절.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fkore\OneDrive\바탕 화면\AntiTest\VibeProject\quotations\sample\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{368B6BDD-475B-4F00-8FD4-542E94C8E2AC}" xr6:coauthVersionLast="41" xr6:coauthVersionMax="41" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1CDB3E3-E2F0-4605-931E-10DBB70B128C}" xr6:coauthVersionLast="41" xr6:coauthVersionMax="41" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="16절" sheetId="3" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="46">
   <si>
     <t>견적일 :</t>
   </si>
@@ -112,9 +112,6 @@
     <t>표지(4도,무광코팅)</t>
   </si>
   <si>
-    <t xml:space="preserve"> * 80 %</t>
-  </si>
-  <si>
     <t>스노우250g</t>
   </si>
   <si>
@@ -122,9 +119,6 @@
   </si>
   <si>
     <t>미색모조80g</t>
-  </si>
-  <si>
-    <t>디지털마스타비</t>
   </si>
   <si>
     <t>소   계</t>
@@ -171,12 +165,16 @@
     <t xml:space="preserve">   견   적   서</t>
     <phoneticPr fontId="15" type="noConversion"/>
   </si>
+  <si>
+    <t>표지디자인</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="17">
+  <numFmts count="18">
     <numFmt numFmtId="176" formatCode="yyyy\.\ mm\.\ dd"/>
     <numFmt numFmtId="177" formatCode="yyyy\.\ m\.\ d"/>
     <numFmt numFmtId="178" formatCode="[$₩-412]#,##0"/>
@@ -194,6 +192,7 @@
     <numFmt numFmtId="190" formatCode="\▽\ #,##0"/>
     <numFmt numFmtId="191" formatCode="&quot;* 3,000 x &quot;\ #,##0\P\ "/>
     <numFmt numFmtId="192" formatCode="\△#,##0"/>
+    <numFmt numFmtId="193" formatCode="&quot;* 1식 × &quot;\ #,##0"/>
   </numFmts>
   <fonts count="16">
     <font>
@@ -204,6 +203,7 @@
     <font>
       <sz val="10"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -1205,7 +1205,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="156">
+  <cellXfs count="158">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
@@ -1309,9 +1309,6 @@
     <xf numFmtId="183" fontId="3" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1346,89 +1343,139 @@
     <xf numFmtId="0" fontId="11" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="70" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="3" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="180" fontId="3" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="12" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="178" fontId="9" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="184" fontId="3" fillId="2" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="188" fontId="3" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="2" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="11" fillId="0" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="11" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="72" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="12" fillId="2" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="69" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="69" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="14" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="70" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="71" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="191" fontId="3" fillId="2" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="12" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="14" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="190" fontId="3" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="12" fillId="2" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="192" fontId="11" fillId="2" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="3" fillId="2" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="182" fontId="3" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="184" fontId="3" fillId="2" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1445,12 +1492,24 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="188" fontId="3" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="3" fontId="12" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="14" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="190" fontId="3" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="12" fillId="2" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="192" fontId="11" fillId="2" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1458,110 +1517,57 @@
     <xf numFmtId="0" fontId="14" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="184" fontId="3" fillId="2" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="70" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="11" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="72" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="12" fillId="2" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="69" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="69" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="14" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="70" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="71" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="191" fontId="3" fillId="2" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="193" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="11" fillId="0" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="180" fontId="3" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="12" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="178" fontId="9" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="176" fontId="3" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="193" fontId="3" fillId="2" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="193" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -1950,13 +1956,13 @@
       <c r="A1" s="1"/>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
-      <c r="D1" s="135" t="s">
-        <v>46</v>
+      <c r="D1" s="51" t="s">
+        <v>44</v>
       </c>
-      <c r="E1" s="136"/>
-      <c r="F1" s="136"/>
-      <c r="G1" s="136"/>
-      <c r="H1" s="137"/>
+      <c r="E1" s="52"/>
+      <c r="F1" s="52"/>
+      <c r="G1" s="52"/>
+      <c r="H1" s="53"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
       <c r="K1" s="2"/>
@@ -1967,11 +1973,11 @@
       <c r="A2" s="5"/>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
-      <c r="D2" s="138"/>
-      <c r="E2" s="139"/>
-      <c r="F2" s="139"/>
-      <c r="G2" s="139"/>
-      <c r="H2" s="140"/>
+      <c r="D2" s="54"/>
+      <c r="E2" s="55"/>
+      <c r="F2" s="55"/>
+      <c r="G2" s="55"/>
+      <c r="H2" s="56"/>
       <c r="I2" s="6"/>
       <c r="J2" s="6"/>
       <c r="K2" s="6"/>
@@ -1997,123 +2003,123 @@
       <c r="A4" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="141">
+      <c r="B4" s="57">
         <v>46190</v>
       </c>
-      <c r="C4" s="88"/>
+      <c r="C4" s="58"/>
       <c r="D4" s="13"/>
-      <c r="E4" s="142" t="s">
-        <v>41</v>
+      <c r="E4" s="59" t="s">
+        <v>39</v>
       </c>
-      <c r="F4" s="51" t="s">
-        <v>42</v>
+      <c r="F4" s="50" t="s">
+        <v>40</v>
       </c>
-      <c r="G4" s="146" t="s">
+      <c r="G4" s="63" t="s">
         <v>1</v>
       </c>
-      <c r="H4" s="147"/>
+      <c r="H4" s="64"/>
       <c r="I4" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="J4" s="148" t="s">
+      <c r="J4" s="65" t="s">
         <v>3</v>
       </c>
-      <c r="K4" s="149"/>
-      <c r="L4" s="84"/>
+      <c r="K4" s="66"/>
+      <c r="L4" s="67"/>
       <c r="M4" s="15"/>
     </row>
     <row r="5" spans="1:13" ht="30" customHeight="1">
-      <c r="A5" s="150" t="s">
+      <c r="A5" s="68" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="88"/>
+      <c r="B5" s="58"/>
       <c r="C5" s="16" t="s">
         <v>5</v>
       </c>
       <c r="D5" s="17"/>
-      <c r="E5" s="143"/>
+      <c r="E5" s="60"/>
       <c r="F5" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="G5" s="92" t="s">
+        <v>6</v>
+      </c>
+      <c r="H5" s="93"/>
+      <c r="I5" s="93"/>
+      <c r="J5" s="93"/>
+      <c r="K5" s="93"/>
+      <c r="L5" s="94"/>
+      <c r="M5" s="19"/>
+    </row>
+    <row r="6" spans="1:13" ht="30" customHeight="1">
+      <c r="A6" s="71" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="72"/>
+      <c r="C6" s="58"/>
+      <c r="D6" s="20"/>
+      <c r="E6" s="61"/>
+      <c r="F6" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="G6" s="92" t="s">
+        <v>9</v>
+      </c>
+      <c r="H6" s="95"/>
+      <c r="I6" s="95"/>
+      <c r="J6" s="95"/>
+      <c r="K6" s="95"/>
+      <c r="L6" s="94"/>
+      <c r="M6" s="19"/>
+    </row>
+    <row r="7" spans="1:13" ht="30" customHeight="1">
+      <c r="A7" s="69" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="73" t="str">
+        <f>NUMBERSTRING(B8,1)&amp;"원정"</f>
+        <v>일백사십일만육천팔백원정</v>
+      </c>
+      <c r="C7" s="74"/>
+      <c r="D7" s="21"/>
+      <c r="E7" s="60"/>
+      <c r="F7" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="G5" s="128" t="s">
-        <v>6</v>
-      </c>
-      <c r="H5" s="129"/>
-      <c r="I5" s="129"/>
-      <c r="J5" s="129"/>
-      <c r="K5" s="129"/>
-      <c r="L5" s="60"/>
-      <c r="M5" s="19"/>
-    </row>
-    <row r="6" spans="1:13" ht="30" customHeight="1">
-      <c r="A6" s="153" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" s="109"/>
-      <c r="C6" s="88"/>
-      <c r="D6" s="20"/>
-      <c r="E6" s="144"/>
-      <c r="F6" s="18" t="s">
-        <v>44</v>
-      </c>
-      <c r="G6" s="128" t="s">
-        <v>9</v>
-      </c>
-      <c r="H6" s="130"/>
-      <c r="I6" s="130"/>
-      <c r="J6" s="130"/>
-      <c r="K6" s="130"/>
-      <c r="L6" s="60"/>
-      <c r="M6" s="19"/>
-    </row>
-    <row r="7" spans="1:13" ht="30" customHeight="1">
-      <c r="A7" s="151" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7" s="154" t="str">
-        <f>NUMBERSTRING(B8,1)&amp;"원정"</f>
-        <v>일백오십사만삼천삼백원정</v>
-      </c>
-      <c r="C7" s="155"/>
-      <c r="D7" s="21"/>
-      <c r="E7" s="143"/>
-      <c r="F7" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="G7" s="131" t="s">
+      <c r="G7" s="96" t="s">
         <v>11</v>
       </c>
-      <c r="H7" s="132"/>
+      <c r="H7" s="97"/>
       <c r="I7" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="J7" s="131" t="s">
+      <c r="J7" s="96" t="s">
         <v>13</v>
       </c>
-      <c r="K7" s="129"/>
-      <c r="L7" s="60"/>
+      <c r="K7" s="93"/>
+      <c r="L7" s="94"/>
       <c r="M7" s="23"/>
     </row>
     <row r="8" spans="1:13" ht="30" customHeight="1">
-      <c r="A8" s="152"/>
-      <c r="B8" s="133">
+      <c r="A8" s="70"/>
+      <c r="B8" s="98">
         <f>J12</f>
-        <v>1543300</v>
+        <v>1416800</v>
       </c>
-      <c r="C8" s="88"/>
+      <c r="C8" s="58"/>
       <c r="D8" s="24"/>
-      <c r="E8" s="145"/>
+      <c r="E8" s="62"/>
       <c r="F8" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="G8" s="66" t="s">
+      <c r="G8" s="99" t="s">
         <v>15</v>
       </c>
-      <c r="H8" s="134"/>
-      <c r="I8" s="134"/>
-      <c r="J8" s="134"/>
-      <c r="K8" s="134"/>
-      <c r="L8" s="67"/>
+      <c r="H8" s="100"/>
+      <c r="I8" s="100"/>
+      <c r="J8" s="100"/>
+      <c r="K8" s="100"/>
+      <c r="L8" s="101"/>
       <c r="M8" s="26"/>
     </row>
     <row r="9" spans="1:13" ht="17.25">
@@ -2132,89 +2138,89 @@
       <c r="M9" s="4"/>
     </row>
     <row r="10" spans="1:13" ht="18.75" customHeight="1">
-      <c r="A10" s="116" t="s">
+      <c r="A10" s="75" t="s">
         <v>16</v>
       </c>
-      <c r="B10" s="105" t="s">
+      <c r="B10" s="108" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="106"/>
-      <c r="D10" s="107"/>
-      <c r="E10" s="110" t="s">
+      <c r="C10" s="109"/>
+      <c r="D10" s="110"/>
+      <c r="E10" s="112" t="s">
         <v>18</v>
       </c>
-      <c r="F10" s="112" t="s">
+      <c r="F10" s="114" t="s">
         <v>14</v>
       </c>
-      <c r="G10" s="106"/>
-      <c r="H10" s="107"/>
-      <c r="I10" s="113" t="s">
+      <c r="G10" s="109"/>
+      <c r="H10" s="110"/>
+      <c r="I10" s="115" t="s">
         <v>19</v>
       </c>
-      <c r="J10" s="114">
+      <c r="J10" s="116">
         <v>230</v>
       </c>
-      <c r="K10" s="106"/>
-      <c r="L10" s="115"/>
+      <c r="K10" s="109"/>
+      <c r="L10" s="117"/>
       <c r="M10" s="31"/>
     </row>
     <row r="11" spans="1:13" ht="18.75" customHeight="1">
-      <c r="A11" s="97"/>
-      <c r="B11" s="108"/>
-      <c r="C11" s="109"/>
-      <c r="D11" s="86"/>
-      <c r="E11" s="111"/>
-      <c r="F11" s="108"/>
-      <c r="G11" s="109"/>
-      <c r="H11" s="86"/>
-      <c r="I11" s="111"/>
-      <c r="J11" s="108"/>
-      <c r="K11" s="109"/>
-      <c r="L11" s="78"/>
+      <c r="A11" s="76"/>
+      <c r="B11" s="111"/>
+      <c r="C11" s="72"/>
+      <c r="D11" s="105"/>
+      <c r="E11" s="113"/>
+      <c r="F11" s="111"/>
+      <c r="G11" s="72"/>
+      <c r="H11" s="105"/>
+      <c r="I11" s="113"/>
+      <c r="J11" s="111"/>
+      <c r="K11" s="72"/>
+      <c r="L11" s="107"/>
       <c r="M11" s="31"/>
     </row>
     <row r="12" spans="1:13" ht="18.75" customHeight="1">
-      <c r="A12" s="117" t="s">
+      <c r="A12" s="77" t="s">
         <v>20</v>
       </c>
-      <c r="B12" s="72" t="str">
+      <c r="B12" s="79" t="str">
         <f>A5</f>
         <v>한국조세재정연구원</v>
       </c>
-      <c r="C12" s="53"/>
-      <c r="D12" s="54"/>
-      <c r="E12" s="122" t="s">
+      <c r="C12" s="80"/>
+      <c r="D12" s="81"/>
+      <c r="E12" s="85" t="s">
         <v>21</v>
       </c>
-      <c r="F12" s="124">
+      <c r="F12" s="87">
         <v>30</v>
       </c>
-      <c r="G12" s="53"/>
-      <c r="H12" s="54"/>
-      <c r="I12" s="125" t="s">
+      <c r="G12" s="80"/>
+      <c r="H12" s="81"/>
+      <c r="I12" s="88" t="s">
         <v>22</v>
       </c>
-      <c r="J12" s="126">
+      <c r="J12" s="89">
         <f>I33</f>
-        <v>1543300</v>
+        <v>1416800</v>
       </c>
-      <c r="K12" s="53"/>
-      <c r="L12" s="102"/>
+      <c r="K12" s="80"/>
+      <c r="L12" s="90"/>
       <c r="M12" s="32"/>
     </row>
     <row r="13" spans="1:13" ht="18.75" customHeight="1">
-      <c r="A13" s="118"/>
-      <c r="B13" s="119"/>
-      <c r="C13" s="120"/>
-      <c r="D13" s="121"/>
-      <c r="E13" s="123"/>
-      <c r="F13" s="119"/>
-      <c r="G13" s="120"/>
-      <c r="H13" s="121"/>
-      <c r="I13" s="123"/>
-      <c r="J13" s="119"/>
-      <c r="K13" s="120"/>
-      <c r="L13" s="127"/>
+      <c r="A13" s="78"/>
+      <c r="B13" s="82"/>
+      <c r="C13" s="83"/>
+      <c r="D13" s="84"/>
+      <c r="E13" s="86"/>
+      <c r="F13" s="82"/>
+      <c r="G13" s="83"/>
+      <c r="H13" s="84"/>
+      <c r="I13" s="86"/>
+      <c r="J13" s="82"/>
+      <c r="K13" s="83"/>
+      <c r="L13" s="91"/>
       <c r="M13" s="32"/>
     </row>
     <row r="14" spans="1:13" ht="16.5" customHeight="1">
@@ -2236,29 +2242,29 @@
       <c r="A15" s="34" t="s">
         <v>23</v>
       </c>
-      <c r="B15" s="90" t="s">
+      <c r="B15" s="123" t="s">
         <v>24</v>
       </c>
-      <c r="C15" s="91"/>
-      <c r="D15" s="90" t="s">
+      <c r="C15" s="124"/>
+      <c r="D15" s="123" t="s">
         <v>25</v>
       </c>
-      <c r="E15" s="92"/>
-      <c r="F15" s="92"/>
-      <c r="G15" s="92"/>
-      <c r="H15" s="91"/>
-      <c r="I15" s="93" t="s">
+      <c r="E15" s="125"/>
+      <c r="F15" s="125"/>
+      <c r="G15" s="125"/>
+      <c r="H15" s="124"/>
+      <c r="I15" s="126" t="s">
         <v>26</v>
       </c>
-      <c r="J15" s="91"/>
-      <c r="K15" s="90" t="s">
+      <c r="J15" s="124"/>
+      <c r="K15" s="123" t="s">
         <v>27</v>
       </c>
-      <c r="L15" s="94"/>
+      <c r="L15" s="127"/>
       <c r="M15" s="19"/>
     </row>
     <row r="16" spans="1:13" ht="26.25" customHeight="1">
-      <c r="A16" s="95" t="s">
+      <c r="A16" s="128" t="s">
         <v>28</v>
       </c>
       <c r="B16" s="35" t="s">
@@ -2268,338 +2274,337 @@
       <c r="D16" s="37">
         <v>15370</v>
       </c>
-      <c r="E16" s="87">
+      <c r="E16" s="121">
         <f>IF(F12&gt;50,F12-50,0)</f>
         <v>0</v>
       </c>
-      <c r="F16" s="88"/>
+      <c r="F16" s="58"/>
       <c r="G16" s="38">
         <v>18</v>
       </c>
-      <c r="H16" s="39" t="s">
-        <v>30</v>
+      <c r="H16" s="43">
+        <v>80</v>
       </c>
-      <c r="I16" s="85">
+      <c r="I16" s="104">
         <f>(D16+((E16/10)*183))*G16*80%</f>
         <v>221328</v>
       </c>
-      <c r="J16" s="86"/>
-      <c r="K16" s="98" t="s">
+      <c r="J16" s="105"/>
+      <c r="K16" s="130" t="s">
+        <v>30</v>
+      </c>
+      <c r="L16" s="107"/>
+      <c r="M16" s="19"/>
+    </row>
+    <row r="17" spans="1:13" ht="26.25" customHeight="1">
+      <c r="A17" s="129"/>
+      <c r="B17" s="39" t="s">
         <v>31</v>
       </c>
-      <c r="L16" s="78"/>
-      <c r="M16" s="19"/>
-    </row>
-    <row r="17" spans="1:13" ht="26.25" customHeight="1">
-      <c r="A17" s="96"/>
-      <c r="B17" s="40" t="s">
-        <v>32</v>
-      </c>
-      <c r="C17" s="41"/>
-      <c r="D17" s="89">
+      <c r="C17" s="40"/>
+      <c r="D17" s="122">
         <v>2380</v>
       </c>
-      <c r="E17" s="88"/>
-      <c r="F17" s="42">
+      <c r="E17" s="58"/>
+      <c r="F17" s="41">
         <f>IF(F12&gt;50,F12-50,0)</f>
         <v>0</v>
       </c>
-      <c r="G17" s="43">
+      <c r="G17" s="42">
         <f>J10</f>
         <v>230</v>
       </c>
-      <c r="H17" s="44">
+      <c r="H17" s="43">
         <v>80</v>
       </c>
-      <c r="I17" s="85">
+      <c r="I17" s="104">
         <f>((8180-D17)+((F17/10)*101))*G17*80%</f>
         <v>1067200</v>
       </c>
-      <c r="J17" s="86"/>
-      <c r="K17" s="77" t="s">
+      <c r="J17" s="105"/>
+      <c r="K17" s="106" t="s">
+        <v>32</v>
+      </c>
+      <c r="L17" s="107"/>
+      <c r="M17" s="19"/>
+    </row>
+    <row r="18" spans="1:13" ht="26.25" hidden="1" customHeight="1">
+      <c r="A18" s="76"/>
+      <c r="B18" s="39" t="s">
+        <v>45</v>
+      </c>
+      <c r="C18" s="40"/>
+      <c r="D18" s="155">
+        <v>0</v>
+      </c>
+      <c r="E18" s="156"/>
+      <c r="F18" s="156"/>
+      <c r="G18" s="156"/>
+      <c r="H18" s="157"/>
+      <c r="I18" s="104">
+        <f>D18</f>
+        <v>0</v>
+      </c>
+      <c r="J18" s="105"/>
+      <c r="K18" s="106"/>
+      <c r="L18" s="107"/>
+      <c r="M18" s="19"/>
+    </row>
+    <row r="19" spans="1:13" ht="26.25" customHeight="1">
+      <c r="A19" s="45"/>
+      <c r="B19" s="39"/>
+      <c r="C19" s="40"/>
+      <c r="D19" s="102"/>
+      <c r="E19" s="58"/>
+      <c r="F19" s="103"/>
+      <c r="G19" s="58"/>
+      <c r="H19" s="44"/>
+      <c r="I19" s="104"/>
+      <c r="J19" s="105"/>
+      <c r="K19" s="106"/>
+      <c r="L19" s="107"/>
+      <c r="M19" s="19"/>
+    </row>
+    <row r="20" spans="1:13" ht="26.25" customHeight="1">
+      <c r="A20" s="45"/>
+      <c r="B20" s="39"/>
+      <c r="C20" s="40"/>
+      <c r="D20" s="102"/>
+      <c r="E20" s="58"/>
+      <c r="F20" s="103"/>
+      <c r="G20" s="58"/>
+      <c r="H20" s="44"/>
+      <c r="I20" s="104"/>
+      <c r="J20" s="105"/>
+      <c r="K20" s="106"/>
+      <c r="L20" s="107"/>
+      <c r="M20" s="19"/>
+    </row>
+    <row r="21" spans="1:13" ht="26.25" customHeight="1">
+      <c r="A21" s="45"/>
+      <c r="B21" s="39"/>
+      <c r="C21" s="40"/>
+      <c r="D21" s="102"/>
+      <c r="E21" s="58"/>
+      <c r="F21" s="103"/>
+      <c r="G21" s="58"/>
+      <c r="H21" s="44"/>
+      <c r="I21" s="104"/>
+      <c r="J21" s="105"/>
+      <c r="K21" s="106"/>
+      <c r="L21" s="107"/>
+      <c r="M21" s="19"/>
+    </row>
+    <row r="22" spans="1:13" ht="26.25" customHeight="1">
+      <c r="A22" s="45"/>
+      <c r="B22" s="39"/>
+      <c r="C22" s="40"/>
+      <c r="D22" s="102"/>
+      <c r="E22" s="58"/>
+      <c r="F22" s="103"/>
+      <c r="G22" s="58"/>
+      <c r="H22" s="44"/>
+      <c r="I22" s="104"/>
+      <c r="J22" s="105"/>
+      <c r="K22" s="106"/>
+      <c r="L22" s="107"/>
+      <c r="M22" s="19"/>
+    </row>
+    <row r="23" spans="1:13" ht="26.25" customHeight="1">
+      <c r="A23" s="45"/>
+      <c r="B23" s="39"/>
+      <c r="C23" s="40"/>
+      <c r="D23" s="102"/>
+      <c r="E23" s="58"/>
+      <c r="F23" s="103"/>
+      <c r="G23" s="58"/>
+      <c r="H23" s="44"/>
+      <c r="I23" s="104"/>
+      <c r="J23" s="105"/>
+      <c r="K23" s="106"/>
+      <c r="L23" s="107"/>
+      <c r="M23" s="19"/>
+    </row>
+    <row r="24" spans="1:13" ht="26.25" customHeight="1">
+      <c r="A24" s="45"/>
+      <c r="B24" s="39"/>
+      <c r="C24" s="40"/>
+      <c r="D24" s="102"/>
+      <c r="E24" s="58"/>
+      <c r="F24" s="103"/>
+      <c r="G24" s="58"/>
+      <c r="H24" s="44"/>
+      <c r="I24" s="104"/>
+      <c r="J24" s="105"/>
+      <c r="K24" s="106"/>
+      <c r="L24" s="107"/>
+      <c r="M24" s="19"/>
+    </row>
+    <row r="25" spans="1:13" ht="26.25" customHeight="1">
+      <c r="A25" s="45"/>
+      <c r="B25" s="39"/>
+      <c r="C25" s="40"/>
+      <c r="D25" s="102"/>
+      <c r="E25" s="58"/>
+      <c r="F25" s="103"/>
+      <c r="G25" s="58"/>
+      <c r="H25" s="44"/>
+      <c r="I25" s="104"/>
+      <c r="J25" s="105"/>
+      <c r="K25" s="106"/>
+      <c r="L25" s="107"/>
+      <c r="M25" s="19"/>
+    </row>
+    <row r="26" spans="1:13" ht="26.25" customHeight="1">
+      <c r="A26" s="45"/>
+      <c r="B26" s="39"/>
+      <c r="C26" s="40"/>
+      <c r="D26" s="102"/>
+      <c r="E26" s="58"/>
+      <c r="F26" s="103"/>
+      <c r="G26" s="58"/>
+      <c r="H26" s="44"/>
+      <c r="I26" s="104"/>
+      <c r="J26" s="105"/>
+      <c r="K26" s="106"/>
+      <c r="L26" s="107"/>
+      <c r="M26" s="19"/>
+    </row>
+    <row r="27" spans="1:13" ht="26.25" customHeight="1">
+      <c r="A27" s="45"/>
+      <c r="B27" s="39"/>
+      <c r="C27" s="40"/>
+      <c r="D27" s="102"/>
+      <c r="E27" s="58"/>
+      <c r="F27" s="103"/>
+      <c r="G27" s="58"/>
+      <c r="H27" s="44"/>
+      <c r="I27" s="104"/>
+      <c r="J27" s="105"/>
+      <c r="K27" s="106"/>
+      <c r="L27" s="107"/>
+      <c r="M27" s="19"/>
+    </row>
+    <row r="28" spans="1:13" ht="26.25" customHeight="1">
+      <c r="A28" s="148" t="s">
         <v>33</v>
       </c>
-      <c r="L17" s="78"/>
-      <c r="M17" s="19"/>
-    </row>
-    <row r="18" spans="1:13" ht="26.25" customHeight="1">
-      <c r="A18" s="97"/>
-      <c r="B18" s="40" t="s">
+      <c r="B28" s="119"/>
+      <c r="C28" s="120"/>
+      <c r="D28" s="118"/>
+      <c r="E28" s="119"/>
+      <c r="F28" s="119"/>
+      <c r="G28" s="119"/>
+      <c r="H28" s="120"/>
+      <c r="I28" s="131">
+        <f>SUM(I16:J27)</f>
+        <v>1288528</v>
+      </c>
+      <c r="J28" s="120"/>
+      <c r="K28" s="139"/>
+      <c r="L28" s="94"/>
+      <c r="M28" s="46"/>
+    </row>
+    <row r="29" spans="1:13" ht="26.25" customHeight="1">
+      <c r="A29" s="149" t="s">
         <v>34</v>
       </c>
-      <c r="C18" s="41"/>
-      <c r="D18" s="89" t="str">
-        <f>CONCATENATE(J10,"P * 500")</f>
-        <v>230P * 500</v>
+      <c r="B29" s="119"/>
+      <c r="C29" s="120"/>
+      <c r="D29" s="150">
+        <v>1</v>
       </c>
-      <c r="E18" s="88"/>
-      <c r="F18" s="99"/>
-      <c r="G18" s="88"/>
-      <c r="H18" s="45"/>
-      <c r="I18" s="85">
-        <f>J10*500</f>
-        <v>115000</v>
+      <c r="E29" s="119"/>
+      <c r="F29" s="119"/>
+      <c r="G29" s="119"/>
+      <c r="H29" s="120"/>
+      <c r="I29" s="132">
+        <f>ROUND(I28*D29,0)</f>
+        <v>1288528</v>
       </c>
-      <c r="J18" s="86"/>
-      <c r="K18" s="77"/>
-      <c r="L18" s="78"/>
-      <c r="M18" s="19"/>
-    </row>
-    <row r="19" spans="1:13" ht="26.25" customHeight="1">
-      <c r="A19" s="46"/>
-      <c r="B19" s="40"/>
-      <c r="C19" s="41"/>
-      <c r="D19" s="104"/>
-      <c r="E19" s="88"/>
-      <c r="F19" s="99"/>
-      <c r="G19" s="88"/>
-      <c r="H19" s="45"/>
-      <c r="I19" s="85"/>
-      <c r="J19" s="86"/>
-      <c r="K19" s="77"/>
-      <c r="L19" s="78"/>
-      <c r="M19" s="19"/>
-    </row>
-    <row r="20" spans="1:13" ht="26.25" customHeight="1">
-      <c r="A20" s="46"/>
-      <c r="B20" s="40"/>
-      <c r="C20" s="41"/>
-      <c r="D20" s="104"/>
-      <c r="E20" s="88"/>
-      <c r="F20" s="99"/>
-      <c r="G20" s="88"/>
-      <c r="H20" s="45"/>
-      <c r="I20" s="85"/>
-      <c r="J20" s="86"/>
-      <c r="K20" s="77"/>
-      <c r="L20" s="78"/>
-      <c r="M20" s="19"/>
-    </row>
-    <row r="21" spans="1:13" ht="26.25" customHeight="1">
-      <c r="A21" s="46"/>
-      <c r="B21" s="40"/>
-      <c r="C21" s="41"/>
-      <c r="D21" s="104"/>
-      <c r="E21" s="88"/>
-      <c r="F21" s="99"/>
-      <c r="G21" s="88"/>
-      <c r="H21" s="45"/>
-      <c r="I21" s="85"/>
-      <c r="J21" s="86"/>
-      <c r="K21" s="77"/>
-      <c r="L21" s="78"/>
-      <c r="M21" s="19"/>
-    </row>
-    <row r="22" spans="1:13" ht="26.25" customHeight="1">
-      <c r="A22" s="46"/>
-      <c r="B22" s="40"/>
-      <c r="C22" s="41"/>
-      <c r="D22" s="104"/>
-      <c r="E22" s="88"/>
-      <c r="F22" s="99"/>
-      <c r="G22" s="88"/>
-      <c r="H22" s="45"/>
-      <c r="I22" s="85"/>
-      <c r="J22" s="86"/>
-      <c r="K22" s="77"/>
-      <c r="L22" s="78"/>
-      <c r="M22" s="19"/>
-    </row>
-    <row r="23" spans="1:13" ht="26.25" customHeight="1">
-      <c r="A23" s="46"/>
-      <c r="B23" s="40"/>
-      <c r="C23" s="41"/>
-      <c r="D23" s="104"/>
-      <c r="E23" s="88"/>
-      <c r="F23" s="99"/>
-      <c r="G23" s="88"/>
-      <c r="H23" s="45"/>
-      <c r="I23" s="85"/>
-      <c r="J23" s="86"/>
-      <c r="K23" s="77"/>
-      <c r="L23" s="78"/>
-      <c r="M23" s="19"/>
-    </row>
-    <row r="24" spans="1:13" ht="26.25" customHeight="1">
-      <c r="A24" s="46"/>
-      <c r="B24" s="40"/>
-      <c r="C24" s="41"/>
-      <c r="D24" s="104"/>
-      <c r="E24" s="88"/>
-      <c r="F24" s="99"/>
-      <c r="G24" s="88"/>
-      <c r="H24" s="45"/>
-      <c r="I24" s="85"/>
-      <c r="J24" s="86"/>
-      <c r="K24" s="77"/>
-      <c r="L24" s="78"/>
-      <c r="M24" s="19"/>
-    </row>
-    <row r="25" spans="1:13" ht="26.25" customHeight="1">
-      <c r="A25" s="46"/>
-      <c r="B25" s="40"/>
-      <c r="C25" s="41"/>
-      <c r="D25" s="104"/>
-      <c r="E25" s="88"/>
-      <c r="F25" s="99"/>
-      <c r="G25" s="88"/>
-      <c r="H25" s="45"/>
-      <c r="I25" s="85"/>
-      <c r="J25" s="86"/>
-      <c r="K25" s="77"/>
-      <c r="L25" s="78"/>
-      <c r="M25" s="19"/>
-    </row>
-    <row r="26" spans="1:13" ht="26.25" customHeight="1">
-      <c r="A26" s="46"/>
-      <c r="B26" s="40"/>
-      <c r="C26" s="41"/>
-      <c r="D26" s="104"/>
-      <c r="E26" s="88"/>
-      <c r="F26" s="99"/>
-      <c r="G26" s="88"/>
-      <c r="H26" s="45"/>
-      <c r="I26" s="85"/>
-      <c r="J26" s="86"/>
-      <c r="K26" s="77"/>
-      <c r="L26" s="78"/>
-      <c r="M26" s="19"/>
-    </row>
-    <row r="27" spans="1:13" ht="26.25" customHeight="1">
-      <c r="A27" s="46"/>
-      <c r="B27" s="40"/>
-      <c r="C27" s="41"/>
-      <c r="D27" s="104"/>
-      <c r="E27" s="88"/>
-      <c r="F27" s="99"/>
-      <c r="G27" s="88"/>
-      <c r="H27" s="45"/>
-      <c r="I27" s="85"/>
-      <c r="J27" s="86"/>
-      <c r="K27" s="77"/>
-      <c r="L27" s="78"/>
-      <c r="M27" s="19"/>
-    </row>
-    <row r="28" spans="1:13" ht="26.25" customHeight="1">
-      <c r="A28" s="68" t="s">
+      <c r="J29" s="120"/>
+      <c r="K29" s="137"/>
+      <c r="L29" s="94"/>
+      <c r="M29" s="47"/>
+    </row>
+    <row r="30" spans="1:13" ht="26.25" customHeight="1">
+      <c r="A30" s="151" t="s">
         <v>35</v>
       </c>
-      <c r="B28" s="56"/>
-      <c r="C28" s="57"/>
-      <c r="D28" s="55"/>
-      <c r="E28" s="56"/>
-      <c r="F28" s="56"/>
-      <c r="G28" s="56"/>
-      <c r="H28" s="57"/>
-      <c r="I28" s="79">
-        <f>SUM(I16:J27)</f>
-        <v>1403528</v>
-      </c>
-      <c r="J28" s="57"/>
-      <c r="K28" s="103"/>
-      <c r="L28" s="60"/>
-      <c r="M28" s="47"/>
-    </row>
-    <row r="29" spans="1:13" ht="26.25" customHeight="1">
-      <c r="A29" s="69" t="s">
-        <v>36</v>
-      </c>
-      <c r="B29" s="56"/>
-      <c r="C29" s="57"/>
-      <c r="D29" s="70">
-        <v>1</v>
-      </c>
-      <c r="E29" s="56"/>
-      <c r="F29" s="56"/>
-      <c r="G29" s="56"/>
-      <c r="H29" s="57"/>
-      <c r="I29" s="80">
-        <f>ROUND(I28*D29,0)</f>
-        <v>1403528</v>
-      </c>
-      <c r="J29" s="57"/>
-      <c r="K29" s="100"/>
-      <c r="L29" s="60"/>
-      <c r="M29" s="48"/>
-    </row>
-    <row r="30" spans="1:13" ht="26.25" customHeight="1">
-      <c r="A30" s="71" t="s">
-        <v>37</v>
-      </c>
-      <c r="B30" s="53"/>
-      <c r="C30" s="54"/>
-      <c r="D30" s="72"/>
-      <c r="E30" s="53"/>
-      <c r="F30" s="53"/>
-      <c r="G30" s="53"/>
-      <c r="H30" s="54"/>
-      <c r="I30" s="81">
+      <c r="B30" s="80"/>
+      <c r="C30" s="81"/>
+      <c r="D30" s="79"/>
+      <c r="E30" s="80"/>
+      <c r="F30" s="80"/>
+      <c r="G30" s="80"/>
+      <c r="H30" s="81"/>
+      <c r="I30" s="133">
         <f>VALUE(RIGHT(I29,3))</f>
         <v>528</v>
       </c>
-      <c r="J30" s="54"/>
-      <c r="K30" s="101"/>
-      <c r="L30" s="102"/>
-      <c r="M30" s="48"/>
+      <c r="J30" s="81"/>
+      <c r="K30" s="138"/>
+      <c r="L30" s="90"/>
+      <c r="M30" s="47"/>
     </row>
     <row r="31" spans="1:13" ht="26.25" customHeight="1">
-      <c r="A31" s="73" t="s">
+      <c r="A31" s="152" t="s">
+        <v>36</v>
+      </c>
+      <c r="B31" s="153"/>
+      <c r="C31" s="135"/>
+      <c r="D31" s="154"/>
+      <c r="E31" s="153"/>
+      <c r="F31" s="153"/>
+      <c r="G31" s="153"/>
+      <c r="H31" s="135"/>
+      <c r="I31" s="134">
+        <f>I29-I30</f>
+        <v>1288000</v>
+      </c>
+      <c r="J31" s="135"/>
+      <c r="K31" s="136"/>
+      <c r="L31" s="67"/>
+      <c r="M31" s="48"/>
+    </row>
+    <row r="32" spans="1:13" ht="26.25" customHeight="1">
+      <c r="A32" s="140" t="s">
+        <v>37</v>
+      </c>
+      <c r="B32" s="80"/>
+      <c r="C32" s="81"/>
+      <c r="D32" s="118"/>
+      <c r="E32" s="119"/>
+      <c r="F32" s="119"/>
+      <c r="G32" s="119"/>
+      <c r="H32" s="120"/>
+      <c r="I32" s="141">
+        <f>I31*0.1</f>
+        <v>128800</v>
+      </c>
+      <c r="J32" s="120"/>
+      <c r="K32" s="142"/>
+      <c r="L32" s="94"/>
+      <c r="M32" s="49"/>
+    </row>
+    <row r="33" spans="1:13" ht="26.25" customHeight="1">
+      <c r="A33" s="143" t="s">
         <v>38</v>
       </c>
-      <c r="B31" s="74"/>
-      <c r="C31" s="75"/>
-      <c r="D31" s="76"/>
-      <c r="E31" s="74"/>
-      <c r="F31" s="74"/>
-      <c r="G31" s="74"/>
-      <c r="H31" s="75"/>
-      <c r="I31" s="82">
-        <f>I29-I30</f>
-        <v>1403000</v>
+      <c r="B33" s="144"/>
+      <c r="C33" s="145"/>
+      <c r="D33" s="146"/>
+      <c r="E33" s="144"/>
+      <c r="F33" s="144"/>
+      <c r="G33" s="144"/>
+      <c r="H33" s="145"/>
+      <c r="I33" s="147">
+        <f>I31+I32</f>
+        <v>1416800</v>
       </c>
-      <c r="J31" s="75"/>
-      <c r="K31" s="83"/>
-      <c r="L31" s="84"/>
-      <c r="M31" s="49"/>
-    </row>
-    <row r="32" spans="1:13" ht="26.25" customHeight="1">
-      <c r="A32" s="52" t="s">
-        <v>39</v>
-      </c>
-      <c r="B32" s="53"/>
-      <c r="C32" s="54"/>
-      <c r="D32" s="55"/>
-      <c r="E32" s="56"/>
-      <c r="F32" s="56"/>
-      <c r="G32" s="56"/>
-      <c r="H32" s="57"/>
-      <c r="I32" s="58">
-        <f>I31*0.1</f>
-        <v>140300</v>
-      </c>
-      <c r="J32" s="57"/>
-      <c r="K32" s="59"/>
-      <c r="L32" s="60"/>
-      <c r="M32" s="50"/>
-    </row>
-    <row r="33" spans="1:13" ht="26.25" customHeight="1">
-      <c r="A33" s="61" t="s">
-        <v>40</v>
-      </c>
-      <c r="B33" s="62"/>
-      <c r="C33" s="63"/>
-      <c r="D33" s="64"/>
-      <c r="E33" s="62"/>
-      <c r="F33" s="62"/>
-      <c r="G33" s="62"/>
-      <c r="H33" s="63"/>
-      <c r="I33" s="65">
-        <f>I31+I32</f>
-        <v>1543300</v>
-      </c>
-      <c r="J33" s="63"/>
-      <c r="K33" s="66"/>
-      <c r="L33" s="67"/>
+      <c r="J33" s="145"/>
+      <c r="K33" s="99"/>
+      <c r="L33" s="101"/>
       <c r="M33" s="23"/>
     </row>
     <row r="34" spans="1:13" ht="13.5">
@@ -16883,73 +16888,22 @@
       <c r="M985" s="4"/>
     </row>
   </sheetData>
-  <mergeCells count="102">
-    <mergeCell ref="D1:H2"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="E4:E8"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="J4:L4"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="A7:A8"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="B12:D13"/>
-    <mergeCell ref="E12:E13"/>
-    <mergeCell ref="F12:H13"/>
-    <mergeCell ref="I12:I13"/>
-    <mergeCell ref="J12:L13"/>
-    <mergeCell ref="G5:L5"/>
-    <mergeCell ref="G6:L6"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="J7:L7"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="G8:L8"/>
-    <mergeCell ref="D19:E19"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="D20:E20"/>
-    <mergeCell ref="F20:G20"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="I19:J19"/>
-    <mergeCell ref="K19:L19"/>
-    <mergeCell ref="I20:J20"/>
-    <mergeCell ref="B10:D11"/>
-    <mergeCell ref="E10:E11"/>
-    <mergeCell ref="F10:H11"/>
-    <mergeCell ref="I10:I11"/>
-    <mergeCell ref="J10:L11"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="F23:G23"/>
-    <mergeCell ref="F24:G24"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="F26:G26"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="D28:H28"/>
-    <mergeCell ref="D21:E21"/>
-    <mergeCell ref="D22:E22"/>
-    <mergeCell ref="D23:E23"/>
-    <mergeCell ref="D24:E24"/>
-    <mergeCell ref="D25:E25"/>
-    <mergeCell ref="D26:E26"/>
-    <mergeCell ref="D27:E27"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="D17:E17"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="D15:H15"/>
-    <mergeCell ref="I15:J15"/>
-    <mergeCell ref="K15:L15"/>
-    <mergeCell ref="A16:A18"/>
-    <mergeCell ref="I16:J16"/>
-    <mergeCell ref="K16:L16"/>
-    <mergeCell ref="D18:E18"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="I18:J18"/>
-    <mergeCell ref="K18:L18"/>
-    <mergeCell ref="I17:J17"/>
-    <mergeCell ref="K17:L17"/>
-    <mergeCell ref="K20:L20"/>
-    <mergeCell ref="K21:L21"/>
+  <mergeCells count="101">
+    <mergeCell ref="A32:C32"/>
+    <mergeCell ref="D32:H32"/>
+    <mergeCell ref="I32:J32"/>
+    <mergeCell ref="K32:L32"/>
+    <mergeCell ref="A33:C33"/>
+    <mergeCell ref="D33:H33"/>
+    <mergeCell ref="I33:J33"/>
+    <mergeCell ref="K33:L33"/>
+    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="D29:H29"/>
+    <mergeCell ref="A30:C30"/>
+    <mergeCell ref="D30:H30"/>
+    <mergeCell ref="A31:C31"/>
+    <mergeCell ref="D31:H31"/>
     <mergeCell ref="I28:J28"/>
     <mergeCell ref="I29:J29"/>
     <mergeCell ref="I30:J30"/>
@@ -16971,21 +16925,71 @@
     <mergeCell ref="K26:L26"/>
     <mergeCell ref="K27:L27"/>
     <mergeCell ref="K28:L28"/>
-    <mergeCell ref="A32:C32"/>
-    <mergeCell ref="D32:H32"/>
-    <mergeCell ref="I32:J32"/>
-    <mergeCell ref="K32:L32"/>
-    <mergeCell ref="A33:C33"/>
-    <mergeCell ref="D33:H33"/>
-    <mergeCell ref="I33:J33"/>
-    <mergeCell ref="K33:L33"/>
-    <mergeCell ref="A28:C28"/>
-    <mergeCell ref="A29:C29"/>
-    <mergeCell ref="D29:H29"/>
-    <mergeCell ref="A30:C30"/>
-    <mergeCell ref="D30:H30"/>
-    <mergeCell ref="A31:C31"/>
-    <mergeCell ref="D31:H31"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="I16:J16"/>
+    <mergeCell ref="K16:L16"/>
+    <mergeCell ref="I18:J18"/>
+    <mergeCell ref="K18:L18"/>
+    <mergeCell ref="I17:J17"/>
+    <mergeCell ref="K17:L17"/>
+    <mergeCell ref="D18:H18"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="D28:H28"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="D23:E23"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="D27:E27"/>
+    <mergeCell ref="D19:E19"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="F20:G20"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="I19:J19"/>
+    <mergeCell ref="K19:L19"/>
+    <mergeCell ref="I20:J20"/>
+    <mergeCell ref="B10:D11"/>
+    <mergeCell ref="E10:E11"/>
+    <mergeCell ref="F10:H11"/>
+    <mergeCell ref="I10:I11"/>
+    <mergeCell ref="J10:L11"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="D15:H15"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="K15:L15"/>
+    <mergeCell ref="K20:L20"/>
+    <mergeCell ref="K21:L21"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="B12:D13"/>
+    <mergeCell ref="E12:E13"/>
+    <mergeCell ref="F12:H13"/>
+    <mergeCell ref="I12:I13"/>
+    <mergeCell ref="J12:L13"/>
+    <mergeCell ref="G5:L5"/>
+    <mergeCell ref="G6:L6"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="J7:L7"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="G8:L8"/>
+    <mergeCell ref="D1:H2"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="E4:E8"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="J4:L4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="B7:C7"/>
   </mergeCells>
   <phoneticPr fontId="15" type="noConversion"/>
   <printOptions horizontalCentered="1" gridLines="1"/>
